--- a/survey_templates/041_office_organization_feedback_form--survey_templates.xlsx
+++ b/survey_templates/041_office_organization_feedback_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,12 +767,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'fully_supported'}</t>
+          <t>fully_supported</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Fully supported'}</t>
+          <t>Fully supported</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'mostly_supported'}</t>
+          <t>mostly_supported</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Mostly supported'}</t>
+          <t>Mostly supported</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_supported'}</t>
+          <t>somewhat_supported</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat supported'}</t>
+          <t>Somewhat supported</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'not_supported_at_all'}</t>
+          <t>not_supported_at_all</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Not supported at all'}</t>
+          <t>Not supported at all</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'chat'}</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Chat'}</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'monitor'}</t>
+          <t>monitor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Monitor'}</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'keyboard'}</t>
+          <t>keyboard</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Keyboard'}</t>
+          <t>Keyboard</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'mouse'}</t>
+          <t>mouse</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Mouse'}</t>
+          <t>Mouse</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'headset'}</t>
+          <t>headset</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Headset'}</t>
+          <t>Headset</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'printer'}</t>
+          <t>printer</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Printer'}</t>
+          <t>Printer</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'quiet'}</t>
+          <t>quiet</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Quiet'}</t>
+          <t>Quiet</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'loud'}</t>
+          <t>loud</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Loud'}</t>
+          <t>Loud</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
